--- a/data/Mörel-Filet/investment_decision/Filet_district_investment_decision.xlsx
+++ b/data/Mörel-Filet/investment_decision/Filet_district_investment_decision.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,7 +680,7 @@
         <v>46023</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0315087391124339</v>
+        <v>0.04501967632941177</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -694,19 +694,19 @@
         <v>1.542373179180522</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03150877087562506</v>
+        <v>0.04501967632941177</v>
       </c>
       <c r="G7" t="n">
         <v>1.542373179180522</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03150877620904588</v>
+        <v>0.04501967632941177</v>
       </c>
       <c r="I7" t="n">
         <v>0.4697832371290632</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03150873316770188</v>
+        <v>0.04501967632941177</v>
       </c>
       <c r="K7" t="n">
         <v>0.4697832371290632</v>
@@ -717,7 +717,7 @@
         <v>47849</v>
       </c>
       <c r="B8" t="n">
-        <v>0.03175200935236496</v>
+        <v>0.04702164797647058</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -731,19 +731,19 @@
         <v>1.542373179180522</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03175200935236495</v>
+        <v>0.0471402252</v>
       </c>
       <c r="G8" t="n">
         <v>1.542373179180522</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03175200935236494</v>
+        <v>0.04794163058910455</v>
       </c>
       <c r="I8" t="n">
         <v>0.6972810410822627</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03175200935236495</v>
+        <v>0.04754246972025482</v>
       </c>
       <c r="K8" t="n">
         <v>0.6972810410822627</v>
@@ -754,7 +754,7 @@
         <v>49675</v>
       </c>
       <c r="B9" t="n">
-        <v>0.032238679055414</v>
+        <v>0.05494242091764704</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -768,19 +768,19 @@
         <v>1.542373179180522</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03231570438028261</v>
+        <v>0.05494242091764706</v>
       </c>
       <c r="G9" t="n">
         <v>1.542373179180522</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03231624663976923</v>
+        <v>0.05494242091764706</v>
       </c>
       <c r="I9" t="n">
         <v>0.8296279659822813</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03225015366296502</v>
+        <v>0.05494242091764706</v>
       </c>
       <c r="K9" t="n">
         <v>0.8296279659822813</v>
@@ -791,7 +791,7 @@
         <v>51502</v>
       </c>
       <c r="B10" t="n">
-        <v>0.03227963504584498</v>
+        <v>0.05494242091764706</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -805,19 +805,19 @@
         <v>1.542373179180522</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03234858640255352</v>
+        <v>0.05494242091764708</v>
       </c>
       <c r="G10" t="n">
         <v>1.542373179180522</v>
       </c>
       <c r="H10" t="n">
-        <v>0.03234870866287711</v>
+        <v>0.05494242091764706</v>
       </c>
       <c r="I10" t="n">
         <v>0.9156056258535027</v>
       </c>
       <c r="J10" t="n">
-        <v>0.03228465312294893</v>
+        <v>0.05494242091764706</v>
       </c>
       <c r="K10" t="n">
         <v>0.9156056258535027</v>
@@ -828,7 +828,7 @@
         <v>53328</v>
       </c>
       <c r="B11" t="n">
-        <v>0.03244678112062734</v>
+        <v>0.05494242091764706</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -842,19 +842,19 @@
         <v>1.542373179180522</v>
       </c>
       <c r="F11" t="n">
-        <v>0.03258625899204733</v>
+        <v>0.05494242091764706</v>
       </c>
       <c r="G11" t="n">
         <v>1.542373179180522</v>
       </c>
       <c r="H11" t="n">
-        <v>0.03257128437205804</v>
+        <v>0.05494242091764706</v>
       </c>
       <c r="I11" t="n">
         <v>0.9757838650281656</v>
       </c>
       <c r="J11" t="n">
-        <v>0.03252070827472973</v>
+        <v>0.05494242091764706</v>
       </c>
       <c r="K11" t="n">
         <v>0.9757838650281656</v>
@@ -1043,746 +1043,6 @@
       </c>
       <c r="K16" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0.001325671241442356</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Filet</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>175</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.9599195146228362</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.001325672693473952</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.9599195146228362</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.001325672937287475</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.9599195146228362</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.001325670969683179</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.9599195146228362</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0.001336792166696347</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Filet</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>175</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.9599195146228362</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.001336792166696347</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.9599195146228362</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.00133679216669636</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.9599195146228362</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.001336792166696347</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.9599195146228362</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0.001569215501291181</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Filet</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>175</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.9599195146228362</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.001565780173823215</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.9599195146228362</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.001576654029369368</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.9599195146228362</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.001568674883995977</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.9599195146228362</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0.001569215501291181</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Filet</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>175</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.9599195146228362</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.001565780173823215</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.9599195146228362</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.001576654029369368</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.9599195146228362</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.001568674883995977</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.9599195146228362</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0.001569215501291181</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Filet</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>175</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.9599195146228362</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.001565780173823215</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.9599195146228362</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.001576654029369368</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.9599195146228362</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.001568674883995977</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.9599195146228362</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Filet</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>8</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.1111114821428571</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.1111114821428571</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.00317437399752769</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.00317437399752769</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Filet</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>8</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.1111114821428571</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.1111114821428571</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.005568108676835157</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.005568108676835157</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Filet</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>8</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.1111114821428571</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.1111114821428571</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.007497592500024584</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.007497592500024584</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Filet</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>8</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.1111114821428571</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.1111114821428571</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.009121790599025646</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.009121790599025646</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B26" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Filet</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>8</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.1111114821428571</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.1111114821428571</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.01052848410575262</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.01052848410575262</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Filet</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.214190808950086</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.214190808950086</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.006119275175956992</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0.006119275175956992</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B28" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Filet</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.214190808950086</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.214190808950086</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.01073370347341717</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0.01073370347341717</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Filet</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.214190808950086</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.214190808950086</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.01445319036149318</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0.01445319036149318</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Filet</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.214190808950086</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.214190808950086</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.01758417464872413</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0.01758417464872413</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Filet</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.214190808950086</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.214190808950086</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.02029587297494481</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0.02029587297494481</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Filet</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>300</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.002962972857142857</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.002962972857142857</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>8.464997326740505e-05</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>8.464997326740505e-05</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Filet</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>300</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.002962972857142857</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.002962972857142857</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.0001484828980489375</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.0001484828980489375</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B34" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Filet</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>300</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.002962972857142857</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.002962972857142857</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.0001999358000006556</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.0001999358000006556</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Filet</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>300</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.002962972857142857</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.002962972857142857</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.0002432477493073506</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0.0002432477493073506</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Filet</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>300</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.002962972857142857</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.002962972857142857</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.0002807595761534032</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0.0002807595761534032</v>
       </c>
     </row>
   </sheetData>
